--- a/output/pdf_financials_xlsx/MID.UN.xlsx
+++ b/output/pdf_financials_xlsx/MID.UN.xlsx
@@ -431,6 +431,10 @@
   </sheetPr>
   <dimension ref="A1:B135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">

--- a/output/pdf_financials_xlsx/MID.UN.xlsx
+++ b/output/pdf_financials_xlsx/MID.UN.xlsx
@@ -1282,19 +1282,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>10.123906</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>9604.800999999999</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>9648.269</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>2715.236</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>3088.436</v>
       </c>
     </row>
     <row r="35">
@@ -1326,19 +1326,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.0149</v>
+        <v>10.138806</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>9604.800999999999</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>9648.269</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>2715.236</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>3088.436</v>
       </c>
     </row>
     <row r="37">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">

--- a/output/pdf_financials_xlsx/MID.UN.xlsx
+++ b/output/pdf_financials_xlsx/MID.UN.xlsx
@@ -3111,19 +3111,19 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>316.625468</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>427773.313</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>1162208.773</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>944977.689</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>85106.015</v>
       </c>
     </row>
     <row r="116">
@@ -7343,7 +7343,11 @@
           <t>Proceeds from Sale of Investments</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E94" s="5" t="n">
         <v>316.625468</v>
       </c>
